--- a/news_push_data/all_news/cnyes/20260402 鉅亨網新聞.xlsx
+++ b/news_push_data/all_news/cnyes/20260402 鉅亨網新聞.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,22 +451,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>伊朗總統發表致美國民眾公開信：提美伊關係被誤解、並無敵意、非主動發動戰爭 | 鉅亨網 - 美股雷達</t>
+          <t>能源供應持續緊張！韓上調資源安全危機至三級 公家機關車輛改「單雙號限行」 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-04-02 05:55</t>
+          <t>2026-04-02 05:40</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-02T05:55:55+08:00</t>
+          <t>2026-04-02T05:40:02+08:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405109</t>
+          <t>https://news.cnyes.com/news/id/6404935</t>
         </is>
       </c>
     </row>
@@ -478,22 +478,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>〈美股盤後〉FOMO情緒推升 三大指數連二升 台積電ADR續揚 | 鉅亨網 - 美股雷達</t>
+          <t>來硬的！UAE擬聯手美國 武力重開荷姆茲海峽 全球油市震盪 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-04-02 05:55</t>
+          <t>2026-04-02 05:20</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-02T05:55:12+08:00</t>
+          <t>2026-04-02T05:20:02+08:00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405106</t>
+          <t>https://news.cnyes.com/news/id/6405038</t>
         </is>
       </c>
     </row>
@@ -505,22 +505,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>能源供應持續緊張！韓上調資源安全危機至三級 公家機關車輛改「單雙號限行」 | 鉅亨網 - 國際政經</t>
+          <t>北約前景不明 馬克宏東京發言暗批川普：某國政策善變 傷害盟友 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-04-02 05:40</t>
+          <t>2026-04-02 04:10</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-02T05:40:02+08:00</t>
+          <t>2026-04-02T04:10:03+08:00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6404935</t>
+          <t>https://news.cnyes.com/news/id/6405034</t>
         </is>
       </c>
     </row>
@@ -532,22 +532,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>來硬的！UAE擬聯手美國 武力重開荷姆茲海峽 全球油市震盪 | 鉅亨網 - 國際政經</t>
+          <t>亞洲搶買俄油補戰爭缺口！菲律賓睽違6年首進口、南韓加入搶購行列 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-04-02 05:20</t>
+          <t>2026-04-02 04:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-02T05:20:02+08:00</t>
+          <t>2026-04-02T04:00:07+08:00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405038</t>
+          <t>https://news.cnyes.com/news/id/6403581</t>
         </is>
       </c>
     </row>
@@ -559,22 +559,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>北約前景不明 馬克宏東京發言暗批川普：某國政策善變 傷害盟友 | 鉅亨網 - 國際政經</t>
+          <t>運價飛天！亞洲國家瘋狂搶租美國油輪 日租金破30萬美元創史高 運費暴衝五倍 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-04-02 04:10</t>
+          <t>2026-04-02 02:50</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-02T04:10:03+08:00</t>
+          <t>2026-04-02T02:50:04+08:00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405034</t>
+          <t>https://news.cnyes.com/news/id/6405013</t>
         </is>
       </c>
     </row>
@@ -586,22 +586,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>亞洲搶買俄油補戰爭缺口！菲律賓睽違6年首進口、南韓加入搶購行列 | 鉅亨網 - 國際政經</t>
+          <t>戴蒙談美伊戰爭：戰事成敗比市場波動更重要 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-04-02 04:00</t>
+          <t>2026-04-02 02:30</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-02T04:00:07+08:00</t>
+          <t>2026-04-02T02:30:03+08:00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6403581</t>
+          <t>https://news.cnyes.com/news/id/6405064</t>
         </is>
       </c>
     </row>
@@ -613,22 +613,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>運價飛天！亞洲國家瘋狂搶租美國油輪 日租金破30萬美元創史高 運費暴衝五倍 | 鉅亨網 - 國際政經</t>
+          <t>伊朗否認停火說法 打臉川普稱「毫無根據」 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-04-02 02:50</t>
+          <t>2026-04-02 01:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-02T02:50:04+08:00</t>
+          <t>2026-04-02T01:00:05+08:00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405013</t>
+          <t>https://news.cnyes.com/news/id/6404962</t>
         </is>
       </c>
     </row>
@@ -640,22 +640,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>戴蒙談美伊戰爭：戰事成敗比市場波動更重要 | 鉅亨網 - 國際政經</t>
+          <t>不容外部勢力介入！伊朗外長：荷姆茲海峽的未來安排 將完全由伊朗與阿曼共同決定 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-04-02 02:30</t>
+          <t>2026-04-02 00:10</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-02T02:30:03+08:00</t>
+          <t>2026-04-02T00:10:02+08:00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405064</t>
+          <t>https://news.cnyes.com/news/id/6405015</t>
         </is>
       </c>
     </row>
@@ -667,22 +667,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>資金大撤退！印度與台灣ETF創紀錄流出 市場情緒急轉 | 鉅亨網 - 美股雷達</t>
+          <t>義大利小型衛星商Argotec佛州設廠 搶進美國衛星製造市場 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-04-02 02:00</t>
+          <t>2026-04-01 21:30</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-02T02:00:03+08:00</t>
+          <t>2026-04-01T21:30:04+08:00</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405039</t>
+          <t>https://news.cnyes.com/news/id/6404865</t>
         </is>
       </c>
     </row>
@@ -694,22 +694,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>伊朗否認停火說法 打臉川普稱「毫無根據」 | 鉅亨網 - 國際政經</t>
+          <t>川普稱伊朗提出停火 荷姆茲海峽未開放前不考慮 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-04-02 01:00</t>
+          <t>2026-04-01 21:03</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-02T01:00:05+08:00</t>
+          <t>2026-04-01T21:03:42+08:00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6404962</t>
+          <t>https://news.cnyes.com/news/id/6404850</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>不容外部勢力介入！伊朗外長：荷姆茲海峽的未來安排 將完全由伊朗與阿曼共同決定 | 鉅亨網 - 國際政經</t>
+          <t>川普稱考慮退出NATO 不滿盟友未挺伊朗軍事行動 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-04-02 00:10</t>
+          <t>2026-04-01 20:57</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-02T00:10:02+08:00</t>
+          <t>2026-04-01T20:57:23+08:00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6405015</t>
+          <t>https://news.cnyes.com/news/id/6404844</t>
         </is>
       </c>
     </row>
@@ -748,22 +748,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>再次打破傳統！美總統川普將出席最高法院針對「出生公民權」口頭辯論 | 鉅亨網 - 美股雷達</t>
+          <t>伊朗、真主黨、胡塞 再次聯合襲擊以色列 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-04-01 23:00</t>
+          <t>2026-04-01 20:33</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-01T23:00:06+08:00</t>
+          <t>2026-04-01T20:33:56+08:00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6404925</t>
+          <t>https://news.cnyes.com/news/id/6404828</t>
         </is>
       </c>
     </row>
@@ -775,22 +775,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>義大利小型衛星商Argotec佛州設廠 搶進美國衛星製造市場 | 鉅亨網 - 國際政經</t>
+          <t>伊朗衝突外溢至美妝供應鏈，包材、運輸成本齊揚，業者示警終端售價恐上修 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-04-01 21:30</t>
+          <t>2026-04-01 19:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-01T21:30:04+08:00</t>
+          <t>2026-04-01T19:00:32+08:00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6404865</t>
+          <t>https://news.cnyes.com/news/id/6404730</t>
         </is>
       </c>
     </row>
@@ -802,22 +802,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>川普稱伊朗提出停火 荷姆茲海峽未開放前不考慮 | 鉅亨網 - 國際政經</t>
+          <t>比亞迪3月銷量連七月下滑，年減逾兩成，中國車市價格戰壓力未解 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-04-01 21:03</t>
+          <t>2026-04-01 19:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-01T21:03:42+08:00</t>
+          <t>2026-04-01T19:00:31+08:00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6404850</t>
+          <t>https://news.cnyes.com/news/id/6404729</t>
         </is>
       </c>
     </row>
@@ -829,22 +829,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>川普稱考慮退出NATO 不滿盟友未挺伊朗軍事行動 | 鉅亨網 - 國際政經</t>
+          <t>德國7月起調降航空稅，短中長程機票稅負同步下修，航空業樂見但仍喊成本偏高 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-04-01 20:57</t>
+          <t>2026-04-01 19:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-01T20:57:23+08:00</t>
+          <t>2026-04-01T19:00:30+08:00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6404844</t>
+          <t>https://news.cnyes.com/news/id/6404727</t>
         </is>
       </c>
     </row>
@@ -856,22 +856,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>伊朗、真主黨、胡塞 再次聯合襲擊以色列 | 鉅亨網 - 國際政經</t>
+          <t>俄羅斯LNG首季出口年增近9%，歐洲進口反增17%，制裁下能源流向仍未脫鉤 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-04-01 20:33</t>
+          <t>2026-04-01 19:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-01T20:33:56+08:00</t>
+          <t>2026-04-01T19:00:29+08:00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6404828</t>
+          <t>https://news.cnyes.com/news/id/6404726</t>
         </is>
       </c>
     </row>
@@ -883,22 +883,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>伊朗衝突外溢至美妝供應鏈，包材、運輸成本齊揚，業者示警終端售價恐上修 | 鉅亨網 - 國際政經</t>
+          <t>一代人只見一次高點已過？彭博大宗商品分析師Mike McGlone：黃金白銀恐已見頂 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-04-01 19:00</t>
+          <t>2026-04-01 18:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-01T19:00:32+08:00</t>
+          <t>2026-04-01T18:00:02+08:00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6404730</t>
+          <t>https://news.cnyes.com/news/id/6404180</t>
         </is>
       </c>
     </row>
@@ -910,22 +910,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>比亞迪3月銷量連七月下滑，年減逾兩成，中國車市價格戰壓力未解 | 鉅亨網 - 國際政經</t>
+          <t>現代汽車3月南韓電動車銷量年增38%，首季國內新能源車銷售寫新高 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-04-01 19:00</t>
+          <t>2026-04-01 16:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-01T19:00:31+08:00</t>
+          <t>2026-04-01T16:00:07+08:00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6404729</t>
+          <t>https://news.cnyes.com/news/id/6404408</t>
         </is>
       </c>
     </row>
@@ -937,22 +937,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>德國7月起調降航空稅，短中長程機票稅負同步下修，航空業樂見但仍喊成本偏高 | 鉅亨網 - 國際政經</t>
+          <t>Alstom執行長由Martin Sion即刻接任，接棒推進全球軌道交通布局 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-04-01 19:00</t>
+          <t>2026-04-01 15:30</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-01T19:00:30+08:00</t>
+          <t>2026-04-01T15:30:05+08:00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6404727</t>
+          <t>https://news.cnyes.com/news/id/6404385</t>
         </is>
       </c>
     </row>
@@ -964,22 +964,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>俄羅斯LNG首季出口年增近9%，歐洲進口反增17%，制裁下能源流向仍未脫鉤 | 鉅亨網 - 國際政經</t>
+          <t>美伊戰事衝擊供應鏈 日本煉油產能利用率下滑至 72.5% | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-04-01 19:00</t>
+          <t>2026-04-01 15:30</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-01T19:00:29+08:00</t>
+          <t>2026-04-01T15:30:04+08:00</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6404726</t>
+          <t>https://news.cnyes.com/news/id/6404384</t>
         </is>
       </c>
     </row>
@@ -991,22 +991,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>一代人只見一次高點已過？彭博大宗商品分析師Mike McGlone：黃金白銀恐已見頂 | 鉅亨網 - 國際政經</t>
+          <t>VinFast損平時程延後至2027年後，2026年拚交車30萬輛 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-04-01 18:00</t>
+          <t>2026-04-01 15:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-01T18:00:02+08:00</t>
+          <t>2026-04-01T15:00:04+08:00</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6404180</t>
+          <t>https://news.cnyes.com/news/id/6404328</t>
         </is>
       </c>
     </row>
@@ -1018,22 +1018,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>不是漲停!就在漲停的路上!!鈦昇⊕、旺宏⊕、華通⊕、臻鼎、【四月神奇寶貝】開放免費索取 | 鉅亨網 - 專家觀點</t>
+          <t>戴蒙出手拯救「美國夢」小摩供800億美元挺小企業與購屋 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-04-01 17:39</t>
+          <t>2026-04-01 14:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-01T17:39:42+08:00</t>
+          <t>2026-04-01T14:00:08+08:00</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6404612</t>
+          <t>https://news.cnyes.com/news/id/6403502</t>
         </is>
       </c>
     </row>
@@ -1045,22 +1045,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>美伊釋出停戰意願，台股融資大減百億後強勢反彈，底部訊號已明確？ | 鉅亨網 - 台股新聞</t>
+          <t>美軍中東戰損曝光：348人傷、預警機首度被毀、最強航母起火撤出戰場 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-04-01 17:27</t>
+          <t>2026-04-01 13:16</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-01T17:27:50+08:00</t>
+          <t>2026-04-01T13:16:36+08:00</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6404583</t>
+          <t>https://news.cnyes.com/news/id/6403906</t>
         </is>
       </c>
     </row>
@@ -1072,22 +1072,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>【量大強漲股整理】台股報復性反彈下，邁威爾獲輝達投資，潛力股大公開? | 鉅亨網 - 台股新聞</t>
+          <t>美以伊第33天戰況：德黑蘭遇襲 胡塞飛彈又襲以色列 美伊有意停戰 盧比歐稱「已看到終點線」 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-04-01 17:21</t>
+          <t>2026-04-01 12:10</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-01T17:21:23+08:00</t>
+          <t>2026-04-01T12:10:02+08:00</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6404533</t>
+          <t>https://news.cnyes.com/news/id/6403994</t>
         </is>
       </c>
     </row>
@@ -1099,22 +1099,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>現代汽車3月南韓電動車銷量年增38%，首季國內新能源車銷售寫新高 | 鉅亨網 - 國際政經</t>
+          <t>伊朗警告美軍基地「不再安全」 放話全面開打 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-04-01 16:00</t>
+          <t>2026-04-01 12:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-01T16:00:07+08:00</t>
+          <t>2026-04-01T12:00:07+08:00</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6404408</t>
+          <t>https://news.cnyes.com/news/id/6404033</t>
         </is>
       </c>
     </row>
@@ -1126,22 +1126,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Alstom執行長由Martin Sion即刻接任，接棒推進全球軌道交通布局 | 鉅亨網 - 國際政經</t>
+          <t>盧比歐：沒有美國 北約將不復存在！赫格塞斯：川普將在對伊行動結束後就北約未來做決定 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-04-01 15:30</t>
+          <t>2026-04-01 11:50</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-01T15:30:05+08:00</t>
+          <t>2026-04-01T11:50:03+08:00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6404385</t>
+          <t>https://news.cnyes.com/news/id/6404040</t>
         </is>
       </c>
     </row>
@@ -1153,22 +1153,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>美伊戰事衝擊供應鏈 日本煉油產能利用率下滑至 72.5% | 鉅亨網 - 國際政經</t>
+          <t>俄羅斯加速建構「Rassvet」衛星網路 對標Starlink、戰後商用布局同步浮現 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-04-01 15:30</t>
+          <t>2026-04-01 11:30</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-04-01T15:30:04+08:00</t>
+          <t>2026-04-01T11:30:08+08:00</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6404384</t>
+          <t>https://news.cnyes.com/news/id/6404124</t>
         </is>
       </c>
     </row>
@@ -1180,22 +1180,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VinFast損平時程延後至2027年後，2026年拚交車30萬輛 | 鉅亨網 - 國際政經</t>
+          <t>川普釋出中東停火曙光帶動日經指數狂飆近 4%晶片與金融股領軍噴出 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-04-01 15:00</t>
+          <t>2026-04-01 11:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-01T15:00:04+08:00</t>
+          <t>2026-04-01T11:00:13+08:00</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6404328</t>
+          <t>https://news.cnyes.com/news/id/6404055</t>
         </is>
       </c>
     </row>
@@ -1207,22 +1207,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>戴蒙出手拯救「美國夢」小摩供800億美元挺小企業與購屋 | 鉅亨網 - 國際政經</t>
+          <t>小米Xiaomi(1810-HK)電動車3月交付破2萬輛 產能爬坡邁入新階段 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-04-01 14:00</t>
+          <t>2026-04-01 11:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-01T14:00:08+08:00</t>
+          <t>2026-04-01T11:00:11+08:00</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6403502</t>
+          <t>https://news.cnyes.com/news/id/6404053</t>
         </is>
       </c>
     </row>
@@ -1234,22 +1234,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>美軍中東戰損曝光：348人傷、預警機首度被毀、最強航母起火撤出戰場 | 鉅亨網 - 國際政經</t>
+          <t>紐時專欄痛批：巨嬰玩火！川普誤判伊朗情勢 戰略恐引爆全球危機 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-04-01 13:16</t>
+          <t>2026-04-01 11:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-01T13:16:36+08:00</t>
+          <t>2026-04-01T11:00:07+08:00</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6403906</t>
+          <t>https://news.cnyes.com/news/id/6403872</t>
         </is>
       </c>
     </row>
@@ -1261,22 +1261,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>美以伊第33天戰況：德黑蘭遇襲 胡塞飛彈又襲以色列 美伊有意停戰 盧比歐稱「已看到終點線」 | 鉅亨網 - 國際政經</t>
+          <t>伊朗出動無人機 攻擊以色列西門子、AT&amp;T | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-04-01 12:10</t>
+          <t>2026-04-01 10:44</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-01T12:10:02+08:00</t>
+          <t>2026-04-01T10:44:22+08:00</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6403994</t>
+          <t>https://news.cnyes.com/news/id/6403903</t>
         </is>
       </c>
     </row>
@@ -1288,22 +1288,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>伊朗警告美軍基地「不再安全」 放話全面開打 | 鉅亨網 - 國際政經</t>
+          <t>美軍一架F-35隱形戰機墜毀 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-04-01 12:00</t>
+          <t>2026-04-01 10:32</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-01T12:00:07+08:00</t>
+          <t>2026-04-01T10:32:00+08:00</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6404033</t>
+          <t>https://news.cnyes.com/news/id/6403861</t>
         </is>
       </c>
     </row>
@@ -1315,22 +1315,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>盧比歐：沒有美國 北約將不復存在！赫格塞斯：川普將在對伊行動結束後就北約未來做決定 | 鉅亨網 - 國際政經</t>
+          <t>紐時：進攻還是防禦？英國首相如何決定美軍轟炸伊朗 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-04-01 11:50</t>
+          <t>2026-04-01 10:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-01T11:50:03+08:00</t>
+          <t>2026-04-01T10:00:51+08:00</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6404040</t>
+          <t>https://news.cnyes.com/news/id/6403927</t>
         </is>
       </c>
     </row>
@@ -1342,22 +1342,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>俄羅斯加速建構「Rassvet」衛星網路 對標Starlink、戰後商用布局同步浮現 | 鉅亨網 - 國際政經</t>
+          <t>華爾街日報：阿聯準備參戰 助美以武力打通荷姆茲海峽 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-04-01 11:30</t>
+          <t>2026-04-01 09:58</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-01T11:30:08+08:00</t>
+          <t>2026-04-01T09:58:33+08:00</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6404124</t>
+          <t>https://news.cnyes.com/news/id/6403836</t>
         </is>
       </c>
     </row>
@@ -1369,22 +1369,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>川普釋出中東停火曙光帶動日經指數狂飆近 4%晶片與金融股領軍噴出 | 鉅亨網 - 國際政經</t>
+          <t>【豐雲學堂ETF大賞】ETF怎麼配置才賺錢？5大類型差異一次講清楚！收益、債券、AI配置全解析 | 鉅亨網 - 台股新聞</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-04-01 11:00</t>
+          <t>2026-04-01 09:05</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-01T11:00:13+08:00</t>
+          <t>2026-04-01T09:05:00+08:00</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6404055</t>
+          <t>https://news.cnyes.com/news/id/6403656</t>
         </is>
       </c>
     </row>
@@ -1396,22 +1396,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>小米Xiaomi(1810-HK)電動車3月交付破2萬輛 產能爬坡邁入新階段 | 鉅亨網 - 國際政經</t>
+          <t>無視中東衝突升級！韓3月出口額年增48.3%首破800億美元 半導體出口328億美元創史高 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-04-01 11:00</t>
+          <t>2026-04-01 09:01</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-04-01T11:00:11+08:00</t>
+          <t>2026-04-01T09:01:34+08:00</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6404053</t>
+          <t>https://news.cnyes.com/news/id/6403637</t>
         </is>
       </c>
     </row>
@@ -1423,22 +1423,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>紐時專欄痛批：巨嬰玩火！川普誤判伊朗情勢 戰略恐引爆全球危機 | 鉅亨網 - 國際政經</t>
+          <t>川普難以輕易抽身伊朗戰事 專家：荷姆茲海峽短期難恢復通行 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-04-01 11:00</t>
+          <t>2026-04-01 08:49</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-04-01T11:00:07+08:00</t>
+          <t>2026-04-01T08:49:11+08:00</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6403872</t>
+          <t>https://news.cnyes.com/news/id/6403631</t>
         </is>
       </c>
     </row>
@@ -1450,22 +1450,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>行情不等人，資金已經開始卡位產業趨勢 | 鉅亨網 - 專家觀點</t>
+          <t>伊朗宣布：關閉學生宿舍 所有課程轉線上教學 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-04-01 10:46</t>
+          <t>2026-04-01 08:45</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-04-01T10:46:23+08:00</t>
+          <t>2026-04-01T08:45:50+08:00</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6404026</t>
+          <t>https://news.cnyes.com/news/id/6403634</t>
         </is>
       </c>
     </row>
@@ -1477,22 +1477,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>伊朗出動無人機 攻擊以色列西門子、AT&amp;T | 鉅亨網 - 國際政經</t>
+          <t>川普稱美國2至3週內可能結束對伊朗軍事行動戰事仍延燒伊朗揚言報復美企 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-04-01 10:44</t>
+          <t>2026-04-01 08:30</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-04-01T10:44:22+08:00</t>
+          <t>2026-04-01T08:30:07+08:00</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6403903</t>
+          <t>https://news.cnyes.com/news/id/6403614</t>
         </is>
       </c>
     </row>
@@ -1504,22 +1504,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>美軍一架F-35隱形戰機墜毀 | 鉅亨網 - 國際政經</t>
+          <t>伊拉克警方證實 美籍戰地女記者在巴格達遭擄 下落不明 川普政府高度關注 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-04-01 10:32</t>
+          <t>2026-04-01 08:30</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-04-01T10:32:00+08:00</t>
+          <t>2026-04-01T08:30:05+08:00</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6403861</t>
+          <t>https://news.cnyes.com/news/id/6403511</t>
         </is>
       </c>
     </row>
@@ -1531,22 +1531,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>紐時：進攻還是防禦？英國首相如何決定美軍轟炸伊朗 | 鉅亨網 - 國際政經</t>
+          <t>俄羅斯大使：伊朗最高領袖目前人在伊朗 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-04-01 10:00</t>
+          <t>2026-04-01 08:29</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-04-01T10:00:51+08:00</t>
+          <t>2026-04-01T08:29:46+08:00</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6403927</t>
+          <t>https://news.cnyes.com/news/id/6403583</t>
         </is>
       </c>
     </row>
@@ -1558,22 +1558,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>華爾街日報：阿聯準備參戰 助美以武力打通荷姆茲海峽 | 鉅亨網 - 國際政經</t>
+          <t>川普表態：伊朗被打回「石器時代」就停戰 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-04-01 09:58</t>
+          <t>2026-04-01 08:18</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-04-01T09:58:33+08:00</t>
+          <t>2026-04-01T08:18:04+08:00</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6403836</t>
+          <t>https://news.cnyes.com/news/id/6403584</t>
         </is>
       </c>
     </row>
@@ -1585,22 +1585,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>【豐雲學堂ETF大賞】ETF怎麼配置才賺錢？5大類型差異一次講清楚！收益、債券、AI配置全解析 | 鉅亨網 - 台股新聞</t>
+          <t>美海關退稅系統建置進度達60%至85% 4月底可望上線 審核流程最長45天 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-04-01 09:05</t>
+          <t>2026-04-01 08:10</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-04-01T09:05:00+08:00</t>
+          <t>2026-04-01T08:10:22+08:00</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6403656</t>
+          <t>https://news.cnyes.com/news/id/6403486</t>
         </is>
       </c>
     </row>
@@ -1612,22 +1612,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>無視中東衝突升級！韓3月出口額年增48.3%首破800億美元 半導體出口328億美元創史高 | 鉅亨網 - 國際政經</t>
+          <t>美伊透過中間人傳話 伊朗外長：收到美方訊息 但這不是談判 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-04-01 09:01</t>
+          <t>2026-04-01 07:10</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-04-01T09:01:34+08:00</t>
+          <t>2026-04-01T07:10:02+08:00</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6403637</t>
+          <t>https://news.cnyes.com/news/id/6403467</t>
         </is>
       </c>
     </row>
@@ -1639,22 +1639,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>川普難以輕易抽身伊朗戰事 專家：荷姆茲海峽短期難恢復通行 | 鉅亨網 - 國際政經</t>
+          <t>美軍布希號航母增援中東 區域將集結三航母打擊群 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-04-01 08:49</t>
+          <t>2026-04-01 07:05</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-04-01T08:49:11+08:00</t>
+          <t>2026-04-01T07:05:04+08:00</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6403631</t>
+          <t>https://news.cnyes.com/news/id/6403565</t>
         </is>
       </c>
     </row>
@@ -1666,22 +1666,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>伊朗宣布：關閉學生宿舍 所有課程轉線上教學 | 鉅亨網 - 國際政經</t>
+          <t>金融危機來最慘！國際金價3月跌幅創17年之最 但專家說還有翻身機會 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-04-01 08:45</t>
+          <t>2026-04-01 07:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-04-01T08:45:50+08:00</t>
+          <t>2026-04-01T07:00:06+08:00</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6403634</t>
+          <t>https://news.cnyes.com/news/id/6403245</t>
         </is>
       </c>
     </row>
@@ -1693,22 +1693,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>川普稱美國2至3週內可能結束對伊朗軍事行動戰事仍延燒伊朗揚言報復美企 | 鉅亨網 - 國際政經</t>
+          <t>國力大於鯨魚！美國「上帝小組」30年首開會 墨西哥灣油氣開採豁免瀕危物種法 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-04-01 08:30</t>
+          <t>2026-04-01 06:50</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-04-01T08:30:07+08:00</t>
+          <t>2026-04-01T06:50:04+08:00</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6403614</t>
+          <t>https://news.cnyes.com/news/id/6403389</t>
         </is>
       </c>
     </row>
@@ -1720,22 +1720,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>伊拉克警方證實 美籍戰地女記者在巴格達遭擄 下落不明 川普政府高度關注 | 鉅亨網 - 國際政經</t>
+          <t>中國、巴基斯坦提五點倡議 提到荷姆茲海峽 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-04-01 08:30</t>
+          <t>2026-04-01 06:20</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-04-01T08:30:05+08:00</t>
+          <t>2026-04-01T06:20:05+08:00</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6403511</t>
+          <t>https://news.cnyes.com/news/id/6403359</t>
         </is>
       </c>
     </row>
@@ -1747,236 +1747,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>俄羅斯大使：伊朗最高領袖目前人在伊朗 | 鉅亨網 - 國際政經</t>
+          <t>傳統記憶體估值下修不可避免！大摩：DDR4首當其衝 NAND廠商迎來高光時刻 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-04-01 08:29</t>
+          <t>2026-04-01 06:10</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-04-01T08:29:46+08:00</t>
+          <t>2026-04-01T06:10:03+08:00</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
-        <is>
-          <t>https://news.cnyes.com/news/id/6403583</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>鉅亨網</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>川普表態：伊朗被打回「石器時代」就停戰 | 鉅亨網 - 國際政經</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2026-04-01 08:18</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2026-04-01T08:18:04+08:00</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>https://news.cnyes.com/news/id/6403584</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>鉅亨網</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>美海關退稅系統建置進度達60%至85% 4月底可望上線 審核流程最長45天 | 鉅亨網 - 國際政經</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2026-04-01 08:10</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2026-04-01T08:10:22+08:00</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>https://news.cnyes.com/news/id/6403486</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>鉅亨網</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>美伊透過中間人傳話 伊朗外長：收到美方訊息 但這不是談判 | 鉅亨網 - 國際政經</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2026-04-01 07:10</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2026-04-01T07:10:02+08:00</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>https://news.cnyes.com/news/id/6403467</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>鉅亨網</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>美軍布希號航母增援中東 區域將集結三航母打擊群 | 鉅亨網 - 國際政經</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2026-04-01 07:05</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2026-04-01T07:05:04+08:00</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>https://news.cnyes.com/news/id/6403565</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>鉅亨網</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>金融危機來最慘！國際金價3月跌幅創17年之最 但專家說還有翻身機會 | 鉅亨網 - 國際政經</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2026-04-01 07:00</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2026-04-01T07:00:06+08:00</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>https://news.cnyes.com/news/id/6403245</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>鉅亨網</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>國力大於鯨魚！美國「上帝小組」30年首開會 墨西哥灣油氣開採豁免瀕危物種法 | 鉅亨網 - 國際政經</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2026-04-01 06:50</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2026-04-01T06:50:04+08:00</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>https://news.cnyes.com/news/id/6403389</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>鉅亨網</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>中國、巴基斯坦提五點倡議 提到荷姆茲海峽 | 鉅亨網 - 國際政經</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2026-04-01 06:20</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2026-04-01T06:20:05+08:00</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>https://news.cnyes.com/news/id/6403359</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>鉅亨網</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>傳統記憶體估值下修不可避免！大摩：DDR4首當其衝 NAND廠商迎來高光時刻 | 鉅亨網 - 國際政經</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2026-04-01 06:10</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2026-04-01T06:10:03+08:00</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
         <is>
           <t>https://news.cnyes.com/news/id/6400928</t>
         </is>
